--- a/docs/plans/dsh-plugin-tools/dsh-plugin-tool-evidence.xlsx
+++ b/docs/plans/dsh-plugin-tools/dsh-plugin-tool-evidence.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>IAM 6.0.3/6.3 均不支持公共客户端/PKCE</t>
+          <t>厂商 6.0.3/6.3 均不支持公共客户端/PKCE；内部 §02 仅称 PKCE 能力、§08 未答</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>IAM 08：6.0.3/6.3 均不支持</t>
+          <t>厂商 08：6.0.3/6.3 均不支持；内部 §08 未答</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>08 项 6.3 仍“不支持”</t>
+          <t>厂商 08 项 6.3 仍“不支持”</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>IAM 6.0.3 与 6.3.0 的 08 项均为“不支持”；等 PKCE 会阻塞 800 人上线。</t>
+          <t>厂商 6.0.3 与 6.3.0 的 08 项均为“不支持”；内部 §08 未答；等 PKCE 会阻塞 800 人上线。</t>
         </is>
       </c>
     </row>
